--- a/test/test_logbook.xlsx
+++ b/test/test_logbook.xlsx
@@ -1,77 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brunsd01/BBC Dropbox/Domi Bruns/Audience Insight/GAM 2025/7. GAM25_calculation/3 DigiGAM/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411F9240-24FC-0041-A7D2-3B1C06F3BAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="20340" windowHeight="16480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="500" windowWidth="20340" windowHeight="16480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="test_explanation" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="test_explanation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>test number</t>
-  </si>
-  <si>
-    <t>script</t>
-  </si>
-  <si>
-    <t>step</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>timestamp</t>
-  </si>
-  <si>
-    <t>pass/fail</t>
-  </si>
-  <si>
-    <t>check file</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -94,29 +66,97 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -404,38 +444,1451 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="27.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="19.33203125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="28.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="17.6640625" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>test number</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>pass/fail</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>check file</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2_FB_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>adding page_consumptions</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2025-11-07 09:16:25</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2_FB_3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ensuring no weeks were lost during FB factors &amp; page consumption calculation</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-11-07 09:16:25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1_FB_7</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>engagement sql query - metric test</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-11-07 09:16:02</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>/1_FB_7_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1_FB_8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>engagement sql query - page test</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2025-11-07 09:16:03</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1_FB_9</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>engagement sql query</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-11-07 09:16:03</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>/1_FB_9_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1_FB_10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>calculating country %</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-11-07 09:16:06</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1_IG_19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ig_user_insights sql query - user test</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-10-31 15:10:46</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>/1_IG_19_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1_IG_20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ig_user_insights sql query</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2025-10-31 15:11:35</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1_IG_21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025-11-02 09:21:41</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1_IG_22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>final country test</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2025-10-24 13:03:02</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>/1_IG_22_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1_IG_23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>final country test</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-10-24 13:03:02</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>/1_IG_23_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1_IG_24</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>final country test</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-10-24 13:03:02</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1_IG_1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ig_media_insights sql query - user test</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:41:29</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>/1_IG_1_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1_IG_2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ig_media_insights sql query - metric test</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:41:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1_IG_3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ig_media_insights sql query</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:41:35</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1_IG_4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ig_media_metadata sql query - channel test</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:43:52</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>/1_IG_4_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1_IG_5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ig_media_insights sql query</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:43:53</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1_IG_6</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">combining ig_media_insights &amp; ig_media_metadata </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:50:25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1_IG_7</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>bringing IG media level to account level</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:51:02</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1_IG_8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ig_user_insights sql query - user test</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:54:52</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>/1_IG_8_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1_IG_9</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ig_user_insights sql query - metric test</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:54:52</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1_IG_11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>get unique user entries per channel &amp; week</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:55:31</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1_IG_12</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>joining user insights to media insights</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:56:36</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>/1_IG_12_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1_IG_13</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ig_user_metadata sql query - user test</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:56:44</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>/1_IG_13_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1_IG_10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ig_user_insights sql query</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:54:52</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1_IG_14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ig_user_insights sql query</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2025-11-01 13:56:44</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1_IG_16</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>final engagement test</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2025-10-31 15:32:57</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1_IG_17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>final engagement test</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025-10-31 15:32:57</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>/1_IG_17_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1_IG_18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>final engagement test</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025-10-31 15:32:57</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>/1_IG_18_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1_TW_10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>joining activity &amp; country - first</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025-10-29 08:13:54</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>/1_TW_10_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1_TW_11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>joining activity &amp; country - second</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2025-10-29 08:13:55</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>/1_TW_11_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1_FB_1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>engagement sql query - page test</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-11-07 09:16:24</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1_FB_2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>engagement sql query - metric test</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025-11-07 09:16:24</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1_FB_3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>engagement sql query</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2025-11-07 09:16:24</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1_YT_6</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2025-11-05 07:52:32</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>/1_YT_6_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1_YT_7</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>testing yt_channel_insights return from redshift</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2025-11-05 07:52:32</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1_YT_8</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>testing yt_channel_insights return from redshift</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2025-11-05 07:52:33</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>/1_YT_8_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1_YT_9</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>calculating % country</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2025-11-05 07:52:36</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1_YT_10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>calculating % country</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>testing merge row count</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2025-11-05 07:52:36</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1_YT_11</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>calculating % country</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>testing country percentage</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2025-11-05 07:52:36</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>/1_YT_11_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1_YT_12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>calculating % country</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for too large values</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2025-11-05 07:52:36</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1_YT_17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>combining country metric</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>testing merge row count</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2025-11-05 07:52:36</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1_Site_1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2025-11-07 09:15:57</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -444,9 +1897,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test/test_logbook.xlsx
+++ b/test/test_logbook.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-11-07 09:16:25</t>
+          <t>2025-11-09 21:20:16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-11-07 09:16:25</t>
+          <t>2025-11-09 21:20:17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-11-07 09:16:02</t>
+          <t>2025-11-09 21:19:55</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-11-07 09:16:03</t>
+          <t>2025-11-09 21:19:55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-11-07 09:16:03</t>
+          <t>2025-11-09 21:19:55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-11-07 09:16:06</t>
+          <t>2025-11-09 21:19:58</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -771,7 +771,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-11-02 09:21:41</t>
+          <t>2025-11-09 21:24:02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-11-01 13:41:29</t>
+          <t>2025-11-09 21:28:07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-11-01 13:41:30</t>
+          <t>2025-11-09 21:28:07</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-11-01 13:41:35</t>
+          <t>2025-11-09 21:28:14</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-11-01 13:43:52</t>
+          <t>2025-11-09 21:29:10</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-11-01 13:43:53</t>
+          <t>2025-11-09 21:29:10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-11-01 13:50:25</t>
+          <t>2025-11-09 21:29:30</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-11-01 13:51:02</t>
+          <t>2025-11-09 21:29:36</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-11-01 13:54:52</t>
+          <t>2025-11-09 21:29:37</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-11-01 13:54:52</t>
+          <t>2025-11-09 21:29:37</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-11-01 13:55:31</t>
+          <t>2025-11-09 21:29:38</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-11-01 13:56:36</t>
+          <t>2025-11-09 21:29:38</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-11-01 13:56:44</t>
+          <t>2025-11-09 21:29:39</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-11-01 13:54:52</t>
+          <t>2025-11-09 21:29:37</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-11-01 13:56:44</t>
+          <t>2025-11-09 21:29:39</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-10-29 08:13:54</t>
+          <t>2025-11-09 21:36:03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-10-29 08:13:55</t>
+          <t>2025-11-09 21:36:03</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-11-07 09:16:24</t>
+          <t>2025-11-09 21:20:15</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-11-07 09:16:24</t>
+          <t>2025-11-09 21:20:16</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-11-07 09:16:24</t>
+          <t>2025-11-09 21:20:16</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1621,7 +1621,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-11-05 07:52:32</t>
+          <t>2025-11-10 10:48:46</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-11-05 07:52:32</t>
+          <t>2025-11-10 10:48:46</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-11-05 07:52:33</t>
+          <t>2025-11-10 10:48:47</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-11-05 07:52:36</t>
+          <t>2025-11-10 10:48:50</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-11-05 07:52:36</t>
+          <t>2025-11-10 10:48:50</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-11-05 07:52:36</t>
+          <t>2025-11-10 10:48:50</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-11-05 07:52:36</t>
+          <t>2025-11-10 10:48:51</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-11-05 07:52:36</t>
+          <t>2025-11-10 10:48:51</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1877,7 +1877,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-11-07 09:15:57</t>
+          <t>2025-11-09 21:13:42</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1886,6 +1886,2837 @@
         </is>
       </c>
       <c r="G44" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1_POD_1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sql returns for all programmes</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:43</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1_POD_2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>sql returns for all programmes</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:43</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>/1_POD_2_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1_POD_3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:45</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1_POD_4</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:45</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1_POD_5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sql returns for individual language services</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:45</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1_POD_6</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:47</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1_POD_7</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sql returns for WSL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:47</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1_POD_8</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:48</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1_POD_9</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sql returns for WS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:48</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1_POD_10</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:49</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1_POD_11</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sql returns for all BBC</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:50</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2_POD_1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>reading in all sql queries</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:54</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1_Site_2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>adding report context info</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:14:24</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1_Site_3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>combining api returns</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:14:33</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1_TW_9</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>stale country dataset - channels</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:35:42</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1_YT_1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>testing automated extracts</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:36:34</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1_YT_2</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:36:34</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>/1_YT_2_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1_YT_3</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:36:34</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>/1_YT_3_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1_YT_4</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:36:35</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1_YT_5</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>testing merge row count</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:36:35</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1_TW_1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sql query tw_accounts_insights - metrics</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:35:55</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1_TW_2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sql query tw_accounts_insights - channels</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:35:55</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>/1_TW_2_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1_TW_3</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>tw_account_insights sql query</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:35:56</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1_TW_4</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>reshaping twitter data to get metric per week &amp; channel</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:35:56</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1_TW_5</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>reshaping activity data</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:35:56</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>/1_TW_5_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1_TW_6</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sql query tw_account_metadata - channels</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:35:57</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>/1_TW_6_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1_TW_7</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>tw_account_metadata sql query</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:35:57</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1_TW_8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">combining activity &amp; metadata </t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:35:57</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>/1_TW_8_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2_POD_2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>reading in all sql queries</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:54</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2_POD_3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>reading in all sql queries</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:55</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2_POD_4</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>reading in all sql queries</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:55</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2_POD_5</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>reading in all sql queries</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:55</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2_POD_6</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>reading in all sql queries</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:56</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2_POD_7</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>adding WSE to ALL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>testing addition of services / platform</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:56</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2_POD_8</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>adding WSE to ANW</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>testing addition of services / platform</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:56</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2_POD_12</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>adding platform</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>testing addition of services / platform</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:56</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2_POD_13</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>adding platform</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>testing addition of services / platform</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:56</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2_POD_14</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>adding higher services</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>testing addition of services / platform</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:57</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2_POD_15</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>adding higher services</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>testing addition of services / platform</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:57</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2_POD_16</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>final_testig_reachDF</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:57</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2_POD_17</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>final_testig_reachDF</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:58</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2_POD_18</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>final_testig_reachDF</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:58</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2_POD_19</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>final_testig_reachDF</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:58</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2_POD_20</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>checking hierarchy for reach</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>testing platform hierarchy reach</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:12:59</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2_site_1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>test all spaces from service are in the raw data</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>testing row counts before/after join</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:15:35</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2_site_2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>test services are in piano raw data</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>testing row counts before/after join</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:15:38</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2_site_3</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>test languages are in piano raw data</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>testing row counts before/after join</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:15:42</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2_site_4</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>test producer nonjs are in piano raw data</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>testing row counts before/after join</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:15:49</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2_site_5</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>test apps are in piano raw data</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>testing row counts before/after join</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:15:58</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2_site_6</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>cleaning &amp; adding placeID</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:17:36</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2_site_7</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>cleaning &amp; adding placeID</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>testing row counts before/after join</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:17:36</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2_site_8</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>final_testig_pianoData</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:17:43</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2_site_9</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>final_testig_pianoData</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:17:44</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2_site_10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>final_testig_pianoData</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:17:45</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2_site_11</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>final_testig_pianoData</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:17:46</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>/2_site_11_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2_site_12</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>adding syndicated GNL data</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:14</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2_site_13</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>final_testig_gnlSyndicationData</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:14</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2_site_14</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>final_testig_gnlSyndicationData</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:14</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2_site_15</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>final_testig_gnlSyndicationData</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:15</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2_site_16</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>final_testig_gnlSyndicationData</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:15</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2_site_17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>final_testig_lePartners</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:15</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2_site_18</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>final_testig_lePartners</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:15</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2_site_19</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>final_testig_lePartners</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:15</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2_site_20</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>final_testig_lePartners</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:15</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>3_site_1</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>adding www to WSE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>testing addition of services / platform</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:48</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>3_site_2</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>adding www to GNL</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>testing addition of services / platform</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:49</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>3_site_3</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>adding www to WOR</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>testing addition of services / platform</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:18:49</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>3_Site_6</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>device factor joining total device and mobile</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>testing row counts before/after join</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:19:01</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>3_Site_7</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>adding WIN to device factor calculation</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>testing addition of services / platform</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:19:10</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>3_Site_8</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>adding WOR to device factor calculation</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>testing addition of services / platform</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:19:11</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>3_Site_10</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>checking hierarchy for m_unique_visitors before device factor is applied</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>testing platform hierarchy reach</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:19:14</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>3_Site_11</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>checking hierarchy for m_unique_visitors before device factor is applied</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>testing platform hierarchy reach</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:19:15</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>3_Site_12</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>checking hierarchy for reach</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>testing platform hierarchy reach</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:19:23</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>/3_Site_12_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>3_Site_13</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>checking hierarchy for reach</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>testing platform hierarchy reach</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:19:25</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>/3_Site_13_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>3_Site_14</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>final_testig_reachDF</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>all weeks in dataset for each group</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:19:27</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>3_Site_15</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>final_testig_reachDF</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:19:27</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>3_Site_16</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>final_testig_reachDF</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:19:27</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>3_Site_17</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>final_testig_reachDF</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:19:28</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1_YT_18</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>merging uv &amp; country</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2025-11-09 21:37:30</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>/1_YT_18_issue_list.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>total_digi_1</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>site_ingest</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>testing no other values than specific occur in col</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2025-11-10 09:15:58</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>total_digi_2</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>site_ingest</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>testing no other values than specific occur in col</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2025-11-10 09:15:58</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>total_digi_3</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>site_ingest</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>testing no other values than specific occur in col</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2025-11-10 09:15:59</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>total_digi_4</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>site_ingest</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>testing no other values than specific occur in col</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2025-11-10 09:15:59</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>total_digi_5</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>social_ingest</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>testing no other values than specific occur in col</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2025-11-10 09:16:02</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>total_digi_6</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>social_ingest</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>testing no other values than specific occur in col</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2025-11-10 09:16:02</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>total_digi_7</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>social_ingest</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>testing no other values than specific occur in col</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2025-11-10 09:16:02</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>total_digi_8</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>social_ingest</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>testing no other values than specific occur in col</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2025-11-10 09:16:02</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
         <is>
           <t>no file created :)</t>
         </is>

--- a/test/test_logbook.xlsx
+++ b/test/test_logbook.xlsx
@@ -1464,7 +1464,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-11-09 21:36:03</t>
+          <t>2025-11-11 17:49:55</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-11-09 21:36:03</t>
+          <t>2025-11-11 17:49:55</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-11-09 21:35:42</t>
+          <t>2025-11-11 17:21:17</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-11-09 21:35:55</t>
+          <t>2025-11-11 17:49:40</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-11-09 21:35:55</t>
+          <t>2025-11-11 17:49:40</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-11-09 21:35:56</t>
+          <t>2025-11-11 17:49:41</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-11-09 21:35:56</t>
+          <t>2025-11-11 17:49:41</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-11-09 21:35:56</t>
+          <t>2025-11-11 17:49:41</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">

--- a/test/test_logbook.xlsx
+++ b/test/test_logbook.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-11-09 21:20:16</t>
+          <t>2025-11-14 11:41:29</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-11-09 21:20:17</t>
+          <t>2025-11-14 15:37:59</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -771,7 +771,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-11-09 21:24:02</t>
+          <t>2025-11-12 15:56:18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-11-09 21:28:07</t>
+          <t>2025-11-12 14:59:47</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-11-09 21:28:07</t>
+          <t>2025-11-12 14:59:47</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-11-09 21:28:14</t>
+          <t>2025-11-12 14:59:53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-11-09 21:29:10</t>
+          <t>2025-11-12 15:00:01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-11-09 21:29:10</t>
+          <t>2025-11-12 15:00:02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-11-09 21:29:30</t>
+          <t>2025-11-12 15:00:24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-11-09 21:29:36</t>
+          <t>2025-11-12 15:00:30</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-11-09 21:29:37</t>
+          <t>2025-11-12 15:00:30</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-11-09 21:29:37</t>
+          <t>2025-11-12 15:00:30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-11-09 21:29:38</t>
+          <t>2025-11-12 15:00:30</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-11-09 21:29:38</t>
+          <t>2025-11-12 15:00:31</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-11-09 21:29:39</t>
+          <t>2025-11-12 15:00:31</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-11-09 21:29:37</t>
+          <t>2025-11-12 15:00:30</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-11-09 21:29:39</t>
+          <t>2025-11-12 15:00:31</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-11-11 17:49:55</t>
+          <t>2025-11-18 17:16:25</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-11-11 17:49:55</t>
+          <t>2025-11-18 17:16:25</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-11-09 21:20:15</t>
+          <t>2025-11-14 15:36:28</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-11-09 21:20:16</t>
+          <t>2025-11-14 15:36:29</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-11-09 21:20:16</t>
+          <t>2025-11-14 15:36:29</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1621,7 +1621,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-11-10 10:48:46</t>
+          <t>2025-11-12 15:01:26</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-11-10 10:48:46</t>
+          <t>2025-11-12 15:01:26</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-11-10 10:48:47</t>
+          <t>2025-11-12 15:01:27</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-11-10 10:48:50</t>
+          <t>2025-11-12 15:01:30</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-11-10 10:48:50</t>
+          <t>2025-11-12 15:01:30</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-11-10 10:48:50</t>
+          <t>2025-11-12 15:01:30</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>/1_YT_11_issue_list.csv</t>
+          <t>no file created :)</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-11-10 10:48:51</t>
+          <t>2025-11-12 15:01:30</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-11-10 10:48:51</t>
+          <t>2025-11-12 15:01:31</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1877,7 +1877,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-11-09 21:13:42</t>
+          <t>2025-11-18 14:23:00</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:43</t>
+          <t>2025-11-18 14:20:24</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:43</t>
+          <t>2025-11-18 14:20:24</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1968,7 +1968,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:45</t>
+          <t>2025-11-18 14:20:30</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1993,7 +1993,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:45</t>
+          <t>2025-11-18 14:20:30</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:45</t>
+          <t>2025-11-18 14:20:30</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2051,7 +2051,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:47</t>
+          <t>2025-11-18 14:20:33</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:47</t>
+          <t>2025-11-18 14:20:33</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2109,7 +2109,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:48</t>
+          <t>2025-11-18 14:20:36</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:48</t>
+          <t>2025-11-18 14:20:36</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2167,7 +2167,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:49</t>
+          <t>2025-11-18 14:20:39</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:50</t>
+          <t>2025-11-18 14:20:39</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:54</t>
+          <t>2025-11-18 14:20:43</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-11-09 21:14:24</t>
+          <t>2025-11-18 14:23:38</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-11-09 21:14:33</t>
+          <t>2025-11-18 14:23:47</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-11-11 17:21:17</t>
+          <t>2025-11-18 17:16:17</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-11-09 21:36:34</t>
+          <t>2025-11-18 17:16:50</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-11-09 21:36:34</t>
+          <t>2025-11-18 17:16:50</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-11-09 21:36:34</t>
+          <t>2025-11-18 17:16:51</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-11-09 21:36:35</t>
+          <t>2025-11-18 17:16:51</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-11-09 21:36:35</t>
+          <t>2025-11-18 17:16:51</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-11-11 17:49:40</t>
+          <t>2025-11-18 17:03:48</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-11-11 17:49:40</t>
+          <t>2025-11-18 17:03:48</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-11-11 17:49:41</t>
+          <t>2025-11-18 17:03:48</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-11-11 17:49:41</t>
+          <t>2025-11-18 17:03:48</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-11-11 17:49:41</t>
+          <t>2025-11-18 17:03:49</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:54</t>
+          <t>2025-11-18 14:20:44</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2827,17 +2827,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:55</t>
+          <t>2025-11-18 14:20:44</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>no file created :)</t>
+          <t>/2_POD_3_issue_list.csv</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:55</t>
+          <t>2025-11-18 14:20:44</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2893,17 +2893,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:55</t>
+          <t>2025-11-18 14:20:45</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>no file created :)</t>
+          <t>/2_POD_5_issue_list.csv</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:56</t>
+          <t>2025-11-18 14:20:45</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:56</t>
+          <t>2025-11-18 14:20:45</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:56</t>
+          <t>2025-11-18 14:20:45</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:56</t>
+          <t>2025-11-18 14:20:45</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:56</t>
+          <t>2025-11-18 14:20:45</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:57</t>
+          <t>2025-11-18 14:20:46</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:57</t>
+          <t>2025-11-18 14:20:46</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:57</t>
+          <t>2025-11-18 14:20:46</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:58</t>
+          <t>2025-11-18 14:20:47</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:58</t>
+          <t>2025-11-18 14:20:47</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:58</t>
+          <t>2025-11-18 14:20:47</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-11-09 21:12:59</t>
+          <t>2025-11-18 14:20:48</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-11-09 21:15:35</t>
+          <t>2025-11-18 14:24:47</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-11-09 21:15:38</t>
+          <t>2025-11-18 14:24:51</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-11-09 21:15:42</t>
+          <t>2025-11-18 14:24:54</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-11-09 21:15:49</t>
+          <t>2025-11-18 14:25:01</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-11-09 21:15:58</t>
+          <t>2025-11-18 14:25:10</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-11-09 21:17:36</t>
+          <t>2025-11-18 14:26:47</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-11-09 21:17:36</t>
+          <t>2025-11-18 14:26:47</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-11-09 21:17:43</t>
+          <t>2025-11-18 14:26:53</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-11-09 21:17:44</t>
+          <t>2025-11-18 14:26:55</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-11-09 21:17:45</t>
+          <t>2025-11-18 14:26:55</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-11-09 21:17:46</t>
+          <t>2025-11-18 14:26:56</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:14</t>
+          <t>2025-11-18 14:27:24</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:14</t>
+          <t>2025-11-18 14:27:24</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:14</t>
+          <t>2025-11-18 14:27:24</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:15</t>
+          <t>2025-11-18 14:27:24</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:15</t>
+          <t>2025-11-18 14:27:24</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:15</t>
+          <t>2025-11-18 14:27:25</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:15</t>
+          <t>2025-11-18 14:27:25</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:15</t>
+          <t>2025-11-18 14:27:25</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:15</t>
+          <t>2025-11-18 14:27:25</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:48</t>
+          <t>2025-11-18 14:27:54</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:49</t>
+          <t>2025-11-18 14:27:55</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025-11-09 21:18:49</t>
+          <t>2025-11-18 14:27:56</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2025-11-09 21:19:01</t>
+          <t>2025-11-18 14:28:07</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2025-11-09 21:37:30</t>
+          <t>2025-11-18 17:16:57</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2025-11-10 09:15:58</t>
+          <t>2025-11-18 18:01:57</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2025-11-10 09:15:58</t>
+          <t>2025-11-18 18:01:57</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2025-11-10 09:15:59</t>
+          <t>2025-11-18 18:01:58</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2025-11-10 09:15:59</t>
+          <t>2025-11-18 18:01:58</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2025-11-10 09:16:02</t>
+          <t>2025-11-18 18:02:01</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2025-11-10 09:16:02</t>
+          <t>2025-11-18 18:02:01</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2025-11-10 09:16:02</t>
+          <t>2025-11-18 18:02:01</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2025-11-10 09:16:02</t>
+          <t>2025-11-18 18:02:02</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">

--- a/test/test_logbook.xlsx
+++ b/test/test_logbook.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,7 +884,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-11-21 16:05:52</t>
+          <t>2025-11-23 10:10:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>../test/issue_lists_2025-11-21/1_INS_engagements_issue_list.csv</t>
+          <t>../test/issue_lists_2025-11-23/1_INS_engagements_issue_list.csv</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-11-21 16:05:52</t>
+          <t>2025-11-23 10:10:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>../test/issue_lists_2025-11-21/2_INS_engagements_issue_list.csv</t>
+          <t>../test/issue_lists_2025-11-23/2_INS_engagements_issue_list.csv</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -948,17 +948,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-11-21 16:05:52</t>
+          <t>2025-11-23 10:10:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>no file created :)</t>
+          <t>../test/issue_lists_2025-11-23/3_INS_engagements_issue_list.csv</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Check no missing values in weekly_reach column from redshift returned</t>
+          <t>Check no missing values in metric columns from redshift returned</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-11-21 16:05:52</t>
+          <t>2025-11-23 10:10:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-11-21 16:23:13</t>
+          <t>2025-11-23 10:12:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1044,27 +1044,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-11-21 16:23:13</t>
+          <t>2025-11-23 12:27:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>no file created :)</t>
+          <t>../test/issue_lists_2025-11-23/6_INS_engagements_issue_list.csv</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>testing inner join - dataloss between two tables</t>
+          <t>testing missing elements in columns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>adding views to reels plays</t>
+          <t>Check that all page IDs are found in SQL</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-11-21 18:15:58</t>
+          <t>2025-11-23 10:09:25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>../test/issue_lists_2025-11-21/1_INS_country_issue_list.csv</t>
+          <t>../test/issue_lists_2025-11-23/1_INS_country_issue_list.csv</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-11-21 18:15:58</t>
+          <t>2025-11-23 10:09:26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>../test/issue_lists_2025-11-21/2_INS_country_issue_list.csv</t>
+          <t>../test/issue_lists_2025-11-23/2_INS_country_issue_list.csv</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-11-21 18:15:59</t>
+          <t>2025-11-23 10:09:26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-11-21 18:15:59</t>
+          <t>2025-11-23 10:09:26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>../test/issue_lists_2025-11-21/4_INS_country_issue_list.csv</t>
+          <t>../test/issue_lists_2025-11-23/4_INS_country_issue_list.csv</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-11-21 18:15:59</t>
+          <t>2025-11-23 10:09:26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>../test/issue_lists_2025-11-21/5_INS_country_issue_list.csv</t>
+          <t>../test/issue_lists_2025-11-23/5_INS_country_issue_list.csv</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-11-21 18:15:59</t>
+          <t>2025-11-23 10:09:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-11-21 18:16:02</t>
+          <t>2025-11-23 10:09:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-11-22 13:22:06</t>
+          <t>2025-11-23 10:50:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2025-11-22 13:22:08</t>
+          <t>2025-11-23 10:50:19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>../test/issue_lists_2025-11-22/3_TWI_combination_issue_list.csv</t>
+          <t>../test/issue_lists_2025-11-23/3_TWI_combination_issue_list.csv</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-11-22 13:22:07</t>
+          <t>2025-11-23 10:50:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>../test/issue_lists_2025-11-22/2_TWI_combination_issue_list.csv</t>
+          <t>../test/issue_lists_2025-11-23/2_TWI_combination_issue_list.csv</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2025-11-22 13:58:47</t>
+          <t>2025-11-23 10:50:36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>../test/issue_lists_2025-11-22/1_YT-_country_issue_list.csv</t>
+          <t>../test/issue_lists_2025-11-23/1_YT-_country_issue_list.csv</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2025-11-22 13:58:48</t>
+          <t>2025-11-23 10:50:37</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>../test/issue_lists_2025-11-22/2_YT-_country_issue_list.csv</t>
+          <t>../test/issue_lists_2025-11-23/2_YT-_country_issue_list.csv</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025-11-22 13:58:48</t>
+          <t>2025-11-23 10:50:37</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>../test/issue_lists_2025-11-22/3_YT-_country_issue_list.csv</t>
+          <t>../test/issue_lists_2025-11-23/3_YT-_country_issue_list.csv</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2025-11-22 13:58:49</t>
+          <t>2025-11-23 10:50:37</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025-11-22 13:58:49</t>
+          <t>2025-11-23 10:50:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025-11-22 13:58:49</t>
+          <t>2025-11-23 10:50:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2041,6 +2041,1798 @@
       <c r="F51" t="inlineStr">
         <is>
           <t>calculating % country</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-11-23 12:27:36</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Testing if lookup DataFrame is empty</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring week tester is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-11-23 12:27:36</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring week tester is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-11-23 12:27:37</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Testing missing values in lookup</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring week tester is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-11-23 12:27:37</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Testing if lookup DataFrame is empty</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring social media accounts is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-11-23 12:27:37</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/4_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring social media accounts is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-11-23 12:27:37</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/5_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Testing missing values in lookup</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring social media accounts is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-11-23 11:36:47</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Testing if lookup DataFrame is empty</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring social media accounts is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-11-23 11:36:47</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring social media accounts is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>8</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-11-23 11:36:48</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Testing missing values in lookup</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring social media accounts is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6_FBE_engagements</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:05:39</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/6_FBE_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Check that all page IDs are found in SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>7_FBE_engagements</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:05:40</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/7_FBE_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Weeks presence per account</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Check all weeks present for each account</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>8_FBE_engagements</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:05:40</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/8_FBE_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Check for NaN and positive values</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Check no missing values in engaged_reach column from redshift returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>9_FBE_engagements</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:05:40</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Check no duplicates from redshift returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>10_FBE_engagements</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:05:40</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>checking social media accounts in lookup, adding service</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>9_FBE_country</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:07:50</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/9_FBE_country_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Check that all page IDs are found in SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>10_FBE_country</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:07:51</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/10_FBE_country_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Weeks presence per account</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Check all weeks present for each account</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>11_FBE_country</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:07:51</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Check for NaN and positive values</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Check no missing values in page fans column from redshift returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>12_FBE_country</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:07:51</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/12_FBE_country_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Check no duplicates from redshift returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>13_FBE_country</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:07:52</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/13_FBE_country_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>calculating country %</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>14_FBE_country</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:07:52</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>calculating country %</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>15_FBE_country</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:07:52</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>testing country percentage</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>summing country % per week &amp; account</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>7_INS_engagements</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-11-23 12:27:40</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/7_INS_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Weeks presence per account</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Check all weeks present for each account</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>6_TWI_engagements</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:25:33</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/6_TWI_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Check that all page IDs are found in SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>7_TWI_engagements</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:25:33</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/7_TWI_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Weeks presence per account</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Check all weeks present for each account</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>8_TWI_engagements</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:25:33</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/8_TWI_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Check for NaN and positive values</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Check no missing values in metric columns column from redshift returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>9_TWI_engagements</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:25:33</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Check no duplicates from redshift returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1_YT_1</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:37:27</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/1_YT_1_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>testing automated extracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1_YT_2</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:40:12</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/1_YT_2_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1_YT_3</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:40:12</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/1_YT_3_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Weeks presence per account</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1_YT_4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:40:12</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1_YT_5</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:40:12</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>testing merge row count</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>7_YT-_engagements</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:44:08</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/7_YT-_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>8_YT-_engagements</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:44:08</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/8_YT-_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Weeks presence per account</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>9_YT-_engagements</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:44:09</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>10_YT-_engagements</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:44:09</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>testing merge row count</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>combine CMS &amp; non CMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>6_YT-_engagements</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:44:08</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/6_YT-_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>all weeks in dataset</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>testing automated extracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>9_TWI_country</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:44:50</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/9_TWI_country_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>checking country in lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>10_TWI_country</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:44:50</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>stale country dataset - channels</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>9_YT-_country</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:52:54</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/9_YT-_country_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>testing missing elements in columns</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Check that all page IDs are found in SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>10_YT-_country</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:52:54</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/10_YT-_country_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Weeks presence per account</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Check all weeks present for each account</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>11_YT-_country</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:52:55</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/11_YT-_country_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Check for NaN and positive values</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Check no missing values in page fans column from redshift returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>12_YT-_country</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:52:55</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Check no duplicates from redshift returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>13_YT-_country</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:52:55</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>adding country codes GAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>14_YT-_country</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:52:55</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>combining country and global views</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>15_YT-_country</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:52:55</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>testing country percentage</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>calculating % country</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>9_TWI_combination</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:57:10</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>10_TWI_combination</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:57:12</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/10_TWI_combination_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>joining activity &amp; country - first</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>11_TWI_combination</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2025-11-23 10:57:12</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/11_TWI_combination_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>joining activity &amp; country - second</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>9</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2025-11-23 11:07:26</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Testing if lookup DataFrame is empty</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring service is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>10</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025-11-23 11:07:26</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring service is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>11</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2025-11-23 11:07:26</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Testing missing values in lookup</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>lookup files - ensuring service is correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1_YT_18</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2025-11-23 11:09:42</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/1_YT_18_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>merging uv &amp; country</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>9_YT-_combination</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2025-11-23 11:11:07</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/9_YT-_combination_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>testing inner join - dataloss between two tables</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>merging uv &amp; country</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>8_INS_engagements</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2025-11-23 12:27:40</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Check for NaN and positive values</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Check no missing values in metric columns from redshift returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>9_INS_engagements</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2025-11-23 12:27:40</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>no file created :)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>testing the combination of columns for uniqueness</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Check no duplicates from redshift returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>10_INS_engagements</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2025-11-23 12:27:40</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/10_INS_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>General outlier detection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Check for extreme outliers in metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>11_INS_engagements</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2025-11-23 12:27:41</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>../test/issue_lists_2025-11-23/11_INS_engagements_issue_list.csv</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Upper-bound outlier detection vs reference</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Compare metrics to reference period</t>
         </is>
       </c>
     </row>
